--- a/Electrical/Electrical_MATERIAL_PRICES_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
+++ b/Electrical/Electrical_MATERIAL_PRICES_BEFORE_FINAL_FIXED_V7_CLEAN.xlsx
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>46287.50796816052</v>
+        <v>46287.50796815972</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="J3" s="7" t="n">
-        <v>46287.50796850958</v>
+        <v>46287.50796850694</v>
       </c>
     </row>
     <row r="4">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>46287.50796776533</v>
+        <v>46287.50796776621</v>
       </c>
     </row>
     <row r="5">
@@ -750,11 +750,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RSI004219228</t>
+          <t>RSI004138083</t>
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>46287.50796816008</v>
+        <v>46288.40346972749</v>
       </c>
     </row>
     <row r="6">
@@ -783,11 +783,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RSI004203947</t>
+          <t>RSI004127896</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
-        <v>46287.50796742234</v>
+        <v>46288.40346836279</v>
       </c>
     </row>
     <row r="7">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="J7" s="7" t="n">
-        <v>46287.50795591256</v>
+        <v>46288.40346879921</v>
       </c>
     </row>
     <row r="8">
@@ -858,11 +858,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>RSI004165482</t>
+          <t>RSI004135168</t>
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>46287.50796126408</v>
+        <v>46288.40346927816</v>
       </c>
     </row>
     <row r="9">
@@ -891,11 +891,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RSI004186573</t>
+          <t>RSI004138083</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>46287.50796420944</v>
+        <v>46288.40346972721</v>
       </c>
     </row>
     <row r="10">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>46287.50795897221</v>
+        <v>46287.50795896991</v>
       </c>
     </row>
     <row r="11">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J11" s="7" t="n">
-        <v>46287.50795897249</v>
+        <v>46287.50795896991</v>
       </c>
     </row>
     <row r="12">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="J12" s="7" t="n">
-        <v>46287.5079589726</v>
+        <v>46287.50795896991</v>
       </c>
     </row>
     <row r="13">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="J13" s="7" t="n">
-        <v>46287.50795982427</v>
+        <v>46287.50795982639</v>
       </c>
     </row>
     <row r="14">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>46287.50795982465</v>
+        <v>46287.50795982639</v>
       </c>
     </row>
     <row r="15">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="J15" s="7" t="n">
-        <v>46287.50796380361</v>
+        <v>46287.50796380787</v>
       </c>
     </row>
     <row r="16">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>46287.50796344238</v>
+        <v>46287.5079634375</v>
       </c>
     </row>
     <row r="17">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="J17" s="7" t="n">
-        <v>46287.50796256581</v>
+        <v>46287.50796256944</v>
       </c>
     </row>
     <row r="18">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>46287.50796344295</v>
+        <v>46287.5079634375</v>
       </c>
     </row>
     <row r="19">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="J19" s="7" t="n">
-        <v>46287.50796344307</v>
+        <v>46287.5079634375</v>
       </c>
     </row>
     <row r="20">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="J20" s="7" t="n">
-        <v>46287.50796344283</v>
+        <v>46287.5079634375</v>
       </c>
     </row>
     <row r="21">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="J21" s="7" t="n">
-        <v>46287.50796256508</v>
+        <v>46287.50796256944</v>
       </c>
     </row>
     <row r="22">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="J22" s="7" t="n">
-        <v>46287.50796344318</v>
+        <v>46287.5079634375</v>
       </c>
     </row>
     <row r="23">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>46287.50796533603</v>
+        <v>46287.50796533565</v>
       </c>
     </row>
     <row r="24">
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="J24" s="7" t="n">
-        <v>46287.50796053932</v>
+        <v>46287.50796054398</v>
       </c>
     </row>
     <row r="25">
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="J25" s="7" t="n">
-        <v>46287.50796646019</v>
+        <v>46287.50796645833</v>
       </c>
     </row>
     <row r="26">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="J26" s="7" t="n">
-        <v>46287.50796091829</v>
+        <v>46287.50796091435</v>
       </c>
     </row>
     <row r="27">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="J27" s="7" t="n">
-        <v>46287.50796091842</v>
+        <v>46287.50796091435</v>
       </c>
     </row>
     <row r="28">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>46287.50796420971</v>
+        <v>46287.50796421296</v>
       </c>
     </row>
     <row r="29">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="J29" s="7" t="n">
-        <v>46287.50796612047</v>
+        <v>46287.50796612268</v>
       </c>
     </row>
     <row r="30">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="J30" s="7" t="n">
-        <v>46287.50796257141</v>
+        <v>46287.50796256944</v>
       </c>
     </row>
     <row r="31">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="J31" s="7" t="n">
-        <v>46287.50796257161</v>
+        <v>46287.50796256944</v>
       </c>
     </row>
     <row r="32">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>46287.50796344269</v>
+        <v>46287.5079634375</v>
       </c>
     </row>
     <row r="33">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>46287.5079634435</v>
+        <v>46287.50796344908</v>
       </c>
     </row>
     <row r="34">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="J34" s="7" t="n">
-        <v>46287.50796380331</v>
+        <v>46287.50796380787</v>
       </c>
     </row>
     <row r="35">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="J35" s="7" t="n">
-        <v>46287.50796459783</v>
+        <v>46287.50796459491</v>
       </c>
     </row>
     <row r="36">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="J36" s="7" t="n">
-        <v>46287.50796459809</v>
+        <v>46287.50796459491</v>
       </c>
     </row>
     <row r="37">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="J37" s="7" t="n">
-        <v>46287.50796533632</v>
+        <v>46287.50796533565</v>
       </c>
     </row>
     <row r="38">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="J38" s="7" t="n">
-        <v>46287.50796568231</v>
+        <v>46287.50796568287</v>
       </c>
     </row>
     <row r="39">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="J39" s="7" t="n">
-        <v>46287.50796612078</v>
+        <v>46287.50796612268</v>
       </c>
     </row>
     <row r="40">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="J40" s="7" t="n">
-        <v>46287.50796612092</v>
+        <v>46287.50796612268</v>
       </c>
     </row>
     <row r="41">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="J41" s="7" t="n">
-        <v>46287.507966121</v>
+        <v>46287.50796612268</v>
       </c>
     </row>
     <row r="42">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J42" s="7" t="n">
-        <v>46287.50796708163</v>
+        <v>46287.50796708334</v>
       </c>
     </row>
   </sheetData>
